--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104729_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104729_W31.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5184</v>
+        <v>2.3979</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3935</v>
+        <v>1.6282</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1249</v>
+        <v>0.7696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2791</v>
+        <v>0.2821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0922</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1844</v>
+        <v>0.1899</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4695</v>
+        <v>0.463</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3577</v>
+        <v>0.3512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1904</v>
+        <v>-0.1808</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.263</v>
+        <v>-0.259</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0726</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5808</v>
+        <v>1.454</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9918</v>
+        <v>1.2352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5891</v>
+        <v>0.2189</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5719</v>
+        <v>2.0398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7376</v>
+        <v>-3.1507</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8343</v>
+        <v>5.1905</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9089</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1427</v>
+        <v>0.5861</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7662</v>
+        <v>0.0475</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2929</v>
+        <v>-1.0619</v>
       </c>
       <c r="K3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1.1029</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.6955</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.1504</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.5039</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.1868</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.2929</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.6161</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.1427</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.4733</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.1359</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.1359</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.3817</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.5553</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1735</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1.0913</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.0913</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.475</v>
+        <v>1.7274</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2956</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7706</v>
+        <v>0.997</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7902</v>
+        <v>1.9052</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2149</v>
+        <v>0.1435</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4247</v>
+        <v>1.7617</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.5099</v>
+        <v>1.288</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2743</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2357</v>
+        <v>1.288</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7198</v>
+        <v>0.6173</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0594</v>
+        <v>0.1435</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6604</v>
+        <v>0.4738</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2719</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5158</v>
+        <v>-0.2265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4863</v>
+        <v>-0.5576</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0296</v>
+        <v>0.3311</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2507</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4475</v>
+        <v>1.5992</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.6948</v>
+        <v>-2.0054</v>
       </c>
       <c r="F5" t="n">
-        <v>5.1423</v>
+        <v>3.6046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6362</v>
+        <v>-0.7911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5876</v>
+        <v>-1.2173</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0486</v>
+        <v>0.4263</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0525</v>
+        <v>-2.5182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0466</v>
+        <v>-2.2795</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0991</v>
+        <v>-0.2388</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6887</v>
+        <v>1.7272</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5409</v>
+        <v>1.0622</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1477</v>
+        <v>0.665</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4991</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1806</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0296</v>
+        <v>1.6375</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>0.7892</v>
       </c>
       <c r="U5" t="n">
-        <v>0.273</v>
+        <v>0.8484</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3375</v>
+        <v>1.0221</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0491</v>
+        <v>-1.0343</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3866</v>
+        <v>2.0564</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8236</v>
+        <v>-0.8212</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5838</v>
+        <v>-1.5825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7603</v>
+        <v>0.7614</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3223</v>
+        <v>-1.3242</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5087</v>
+        <v>-1.5103</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1864</v>
+        <v>0.1862</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4987</v>
+        <v>0.503</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5739</v>
+        <v>0.5752</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9573</v>
+        <v>0.6352</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1138</v>
+        <v>0.1321</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8435</v>
+        <v>0.5032</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1044</v>
+        <v>0.3046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3549</v>
+        <v>-0.6476</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2505</v>
+        <v>0.9522</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4091</v>
+        <v>-1.5316</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0136</v>
+        <v>-1.7344</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4227</v>
+        <v>0.2028</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8164</v>
+        <v>-1.0176</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9528</v>
+        <v>-0.9727</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1364</v>
+        <v>-0.0449</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2255</v>
+        <v>-0.5139</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9392</v>
+        <v>-0.7617</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2863</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2719</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4183</v>
+        <v>-0.8177</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.372</v>
+        <v>-0.3929</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0462</v>
+        <v>-0.4248</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9318</v>
+        <v>2.8814</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1825</v>
+        <v>3.0392</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2507</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5631</v>
+        <v>0.2799</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1879</v>
+        <v>0.5426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6247</v>
+        <v>-0.2627</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5323</v>
+        <v>-0.4089</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7333</v>
+        <v>1.0137</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2011</v>
+        <v>-1.4227</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0102</v>
+        <v>0.8077</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9669</v>
+        <v>1.9478</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0433</v>
+        <v>-1.1401</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5221</v>
+        <v>-1.2166</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7664</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2443</v>
+        <v>-0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0447</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6912</v>
+        <v>-0.2429</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9527</v>
+        <v>-0.1677</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7385</v>
+        <v>-0.0752</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8875</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>3.0469</v>
+        <v>2.1789</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1594</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6024</v>
+        <v>-0.6401</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.963</v>
+        <v>-2.6143</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6394</v>
+        <v>1.9742</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7156</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8821</v>
+        <v>0.928</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1664</v>
+        <v>0.0605</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4283</v>
+        <v>0.881</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0248</v>
+        <v>0.3685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5965</v>
+        <v>0.5125</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2873</v>
+        <v>0.1074</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1427</v>
+        <v>0.5595</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4301</v>
+        <v>-0.4521</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2272</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-4.7803</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9087</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4317</v>
+        <v>0.4005</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4419</v>
+        <v>0.5825</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0102</v>
+        <v>-0.1819</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7699</v>
+        <v>-2.139</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2592</v>
+        <v>-1.445</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4893</v>
+        <v>-0.694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9962</v>
+        <v>-0.7173</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9308999999999999</v>
+        <v>-0.8842</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1669</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8982</v>
+        <v>-0.4319</v>
       </c>
       <c r="K10" t="n">
-        <v>0.375</v>
+        <v>-1.0277</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5232</v>
+        <v>0.5958</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0979</v>
+        <v>-0.2854</v>
       </c>
       <c r="N10" t="n">
-        <v>0.556</v>
+        <v>0.1435</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.458</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7262</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.7709</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0447</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7449</v>
+        <v>-0.1046</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0915</v>
+        <v>-0.0327</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6533</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.705</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0.705</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1696</v>
+        <v>-3.2721</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0293</v>
+        <v>-2.2122</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1403</v>
+        <v>-1.0599</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3851</v>
+        <v>-1.3847</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0076</v>
+        <v>-2.0074</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6227</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4548</v>
+        <v>-1.4616</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.263</v>
+        <v>-2.2655</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8082</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0697</v>
+        <v>0.077</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2554</v>
+        <v>0.2581</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1857</v>
+        <v>-0.1811</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7611</v>
+        <v>0.6573</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8333</v>
+        <v>0.6639</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0722</v>
+        <v>-0.0066</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.847</v>
+        <v>-3.4349</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5356</v>
+        <v>-3.2872</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3113</v>
+        <v>-0.1477</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6287</v>
+        <v>-1.6266</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0782</v>
+        <v>-1.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5506</v>
+        <v>-0.5496</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9357</v>
+        <v>-0.9388</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1841</v>
+        <v>-0.1864</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6931</v>
+        <v>-0.6879</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8551</v>
+        <v>-0.4425</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3281</v>
+        <v>-0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.527</v>
+        <v>-0.3703</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8067</v>
+        <v>-5.7992</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0429</v>
+        <v>-2.8656</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7637</v>
+        <v>-2.9337</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3443</v>
+        <v>-2.3381</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3697</v>
+        <v>-1.3673</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6766</v>
+        <v>-0.6794</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6334</v>
+        <v>-0.6345</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0433</v>
+        <v>-0.0449</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6677</v>
+        <v>-1.6587</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7363</v>
+        <v>-0.7328</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9314</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0833</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0944</v>
+        <v>0.0902</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1777</v>
+        <v>-0.0066</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.303999999999998</v>
+        <v>-5.914400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.5714</v>
+        <v>-16.3612</v>
       </c>
       <c r="F14" t="n">
-        <v>10.2675</v>
+        <v>10.4465</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.8085</v>
+        <v>-5.8102</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.1001</v>
+        <v>-7.1067</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2915</v>
+        <v>1.2966</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.9133</v>
+        <v>-5.993900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.1231</v>
+        <v>-6.168100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2095999999999997</v>
+        <v>0.1741</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1048000000000002</v>
+        <v>0.1840999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9771</v>
+        <v>-0.9385000000000002</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0818</v>
+        <v>1.1225</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.135900000000001</v>
+        <v>-1.138099999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.5829</v>
+        <v>-21.6249</v>
       </c>
       <c r="R14" t="n">
-        <v>20.4467</v>
+        <v>20.4868</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2092</v>
+        <v>3.5994</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1705</v>
+        <v>2.5275</v>
       </c>
       <c r="U14" t="n">
-        <v>1.039</v>
+        <v>1.0725</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5689</v>
+        <v>-2.566</v>
       </c>
       <c r="W14" t="n">
-        <v>8.7546</v>
+        <v>8.7308</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.3235</v>
+        <v>-11.2965</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6811</v>
+        <v>3.5364</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0932</v>
+        <v>3.272</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4122</v>
+        <v>0.2644</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4585</v>
+        <v>3.1828</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6702</v>
+        <v>-0.4048</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2117</v>
+        <v>3.5877</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4829</v>
+        <v>3.9244</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6627</v>
+        <v>-0.4761</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8202</v>
+        <v>4.4005</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0244</v>
+        <v>-0.7416</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0075</v>
+        <v>0.0713</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0319</v>
+        <v>-0.8129</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7262</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4991</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1991</v>
+        <v>-0.2579</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9034</v>
+        <v>-0.077</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2957</v>
+        <v>-0.1808</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2507</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4332</v>
+        <v>1.018</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0428</v>
+        <v>3.043</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1366</v>
+        <v>3.1796</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9062</v>
+        <v>-0.1366</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3877</v>
+        <v>0.4637</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3231</v>
+        <v>0.6718</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0645</v>
+        <v>-0.2081</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1806</v>
+        <v>1.4775</v>
       </c>
       <c r="K16" t="n">
-        <v>1.106</v>
+        <v>0.6583</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.8192</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2071</v>
+        <v>-1.0138</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2171</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>0.99</v>
+        <v>-1.0273</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5903</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5903</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5252</v>
+        <v>1.5597</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.044</v>
+        <v>1.0075</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4812</v>
+        <v>0.5521</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4101</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.4262</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4101</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DUKE JR</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0149</v>
+        <v>2.731</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3059</v>
+        <v>0.7755</v>
       </c>
       <c r="F17" t="n">
-        <v>0.709</v>
+        <v>1.9555</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4589</v>
+        <v>3.3902</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4674</v>
+        <v>2.3233</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0085</v>
+        <v>1.0669</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4203</v>
+        <v>1.1776</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7304</v>
+        <v>1.1032</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3101</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0386</v>
+        <v>2.2126</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.263</v>
+        <v>1.2201</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3016</v>
+        <v>0.9925</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2272</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0447</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3057</v>
+        <v>-0.8476</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8837</v>
+        <v>-0.4021</v>
       </c>
       <c r="U17" t="n">
-        <v>0.422</v>
+        <v>-0.4455</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4775</v>
+        <v>-1.405</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2738</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7963</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>D. DUKE JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4374</v>
+        <v>2.3911</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4719</v>
+        <v>1.5697</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0346</v>
+        <v>0.8214</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1914</v>
+        <v>0.4512</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4042</v>
+        <v>2.4644</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5956</v>
+        <v>-2.0132</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9407</v>
+        <v>0.406</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4718</v>
+        <v>2.7234</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4125</v>
+        <v>-2.3175</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7493</v>
+        <v>0.0452</v>
       </c>
       <c r="N18" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.259</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8169</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6816</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5903</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2719</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3682</v>
+        <v>0.6911</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9023</v>
+        <v>0.1716</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4659</v>
+        <v>0.5195</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0674</v>
+        <v>1.4764</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0238</v>
+        <v>3.2684</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.156</v>
+        <v>2.2349</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6309</v>
+        <v>-0.4195</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7869</v>
+        <v>2.6544</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0856</v>
+        <v>2.0861</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0158</v>
+        <v>1.0165</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0698</v>
+        <v>1.0696</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5455</v>
+        <v>1.5366</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6627</v>
+        <v>0.6583</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8828</v>
+        <v>0.8783</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5402</v>
+        <v>0.5495</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3531</v>
+        <v>0.3583</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1871</v>
+        <v>0.1912</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3187</v>
+        <v>1.4055</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0254</v>
+        <v>0.2598</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2933</v>
+        <v>1.1457</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2863</v>
+        <v>1.8908</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4808</v>
+        <v>-1.8977</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7671</v>
+        <v>3.7885</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7738</v>
+        <v>0.7789</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4771</v>
+        <v>-0.4742</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2509</v>
+        <v>1.2531</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3009</v>
+        <v>-1.305</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1458</v>
+        <v>-1.1484</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1551</v>
+        <v>-0.1566</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0747</v>
+        <v>2.0839</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6686</v>
+        <v>0.6741</v>
       </c>
       <c r="O20" t="n">
-        <v>1.406</v>
+        <v>1.4097</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1456</v>
+        <v>-0.5514</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1799</v>
+        <v>-0.5927</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0343</v>
+        <v>0.0413</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7343</v>
+        <v>1.2022</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3275</v>
+        <v>-3.3445</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0618</v>
+        <v>4.5467</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9747</v>
+        <v>2.9742</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2863</v>
+        <v>2.286</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6884</v>
+        <v>0.6882</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1243</v>
+        <v>0.1167</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9565</v>
+        <v>0.9513</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8345</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8504</v>
+        <v>2.8575</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3298</v>
+        <v>1.3347</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5206</v>
+        <v>1.5228</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4229</v>
+        <v>0.049</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.044</v>
+        <v>-0.0468</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3789</v>
+        <v>0.0958</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6411</v>
+        <v>-1.8597</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8439</v>
+        <v>-3.2704</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2028</v>
+        <v>1.4108</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2303</v>
+        <v>-0.2282</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0113</v>
+        <v>1.0109</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2416</v>
+        <v>-1.2391</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0277</v>
+        <v>-0.0342</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5064</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4787</v>
+        <v>0.4764</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2026</v>
+        <v>-0.194</v>
       </c>
       <c r="N22" t="n">
-        <v>1.5177</v>
+        <v>1.5215</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3427</v>
+        <v>-1.5632</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2493</v>
+        <v>-0.6624</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0933</v>
+        <v>-0.9008</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4</v>
+        <v>-2.9058</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8614</v>
+        <v>-4.6353</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4614</v>
+        <v>1.7294</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7982</v>
+        <v>-2.7933</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4734</v>
+        <v>-1.4707</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3248</v>
+        <v>-1.3226</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0912</v>
+        <v>-2.0938</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.526</v>
+        <v>-1.5276</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5652</v>
+        <v>-0.5662</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.707</v>
+        <v>-0.6995</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0526</v>
+        <v>0.0568</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2152</v>
+        <v>0.2728</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.044</v>
+        <v>0.1901</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1712</v>
+        <v>0.0827</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0077</v>
+        <v>-3.376</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2218</v>
+        <v>-6.7654</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2142</v>
+        <v>3.3894</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4935</v>
+        <v>-4.4956</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3193</v>
+        <v>-0.3163</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.1742</v>
+        <v>-4.1793</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3793</v>
+        <v>-5.3898</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4914</v>
+        <v>-1.4931</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.8879</v>
+        <v>-3.8967</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8858</v>
+        <v>0.8942</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1721</v>
+        <v>1.1768</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2863</v>
+        <v>-0.2826</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0132</v>
+        <v>-1.3843</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3881</v>
+        <v>-0.9203</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6251</v>
+        <v>-0.464</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.304</v>
+        <v>8.8879</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.3587</v>
+        <v>-11.536</v>
       </c>
       <c r="F25" t="n">
-        <v>18.6626</v>
+        <v>20.4239</v>
       </c>
       <c r="G25" t="n">
-        <v>5.808599999999999</v>
+        <v>5.81</v>
       </c>
       <c r="H25" t="n">
-        <v>7.100099999999999</v>
+        <v>7.1069</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2916</v>
+        <v>-1.2968</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1048</v>
+        <v>-0.1840000000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9769000000000001</v>
+        <v>0.9386999999999994</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0817</v>
+        <v>-1.122599999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>5.913500000000001</v>
+        <v>5.994</v>
       </c>
       <c r="N25" t="n">
-        <v>6.123100000000001</v>
+        <v>6.1681</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2097000000000001</v>
+        <v>-0.1741</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.4467</v>
+        <v>-20.4869</v>
       </c>
       <c r="R25" t="n">
-        <v>21.5829</v>
+        <v>21.6249</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.209499999999999</v>
+        <v>-0.6262999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0391</v>
+        <v>-1.0723</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1703</v>
+        <v>0.4459999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5688</v>
+        <v>2.5658</v>
       </c>
       <c r="W25" t="n">
-        <v>10.2321</v>
+        <v>10.2071</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.663499999999999</v>
+        <v>-7.641299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104729_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104729_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.2965</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104729_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.641299999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
